--- a/docs/oc-regiones/gas-licuado-de-petroleo/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/magallanes-y-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M302"/>
+  <dimension ref="A1:M303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4161.26</v>
+        <v>4114.9</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5344.03</v>
+        <v>5337.22</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1826.78</v>
+        <v>1824.46</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1860.61</v>
+        <v>1857.31</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1249.52</v>
+        <v>1247.31</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2745.36</v>
+        <v>2709.88</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1874.31</v>
+        <v>1870.25</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3292.7</v>
+        <v>3285.57</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1098.87</v>
+        <v>1094.26</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1091.66</v>
+        <v>1082.42</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2992.66</v>
+        <v>3024.76</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1246.94</v>
+        <v>1260.32</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1227.46</v>
+        <v>1243.23</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1374.75</v>
+        <v>1392.42</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>490.98</v>
+        <v>497.29</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1031.48</v>
+        <v>1044.73</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>183.29</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>660.09</v>
+        <v>644.65</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>440.06</v>
+        <v>429.77</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2640.37</v>
+        <v>2602.33</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1400.96</v>
+        <v>1380.77</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>628.41</v>
+        <v>620.29</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1562.95</v>
+        <v>1542.75</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>781.47</v>
+        <v>771.37</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>130.25</v>
+        <v>128.56</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1372.05</v>
+        <v>1372.06</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>102.58</v>
+        <v>102.23</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1667.14</v>
+        <v>1661.42</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>4485.56</v>
+        <v>4470.16</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>790.48</v>
+        <v>786.3</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>573.08</v>
+        <v>569.49</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>435.97</v>
+        <v>438.83</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>410.32</v>
+        <v>413.01</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1025.81</v>
+        <v>1039.62</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1974.62</v>
+        <v>2001.21</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>102.58</v>
+        <v>104.14</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1179.68</v>
+        <v>1197.64</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>102.58</v>
+        <v>105.17</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>344.81</v>
+        <v>355.27</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3211.04</v>
+        <v>3308.41</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5369.63</v>
+        <v>5529.23</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1255.68</v>
+        <v>1251.21</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5506.33</v>
+        <v>5522.28</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1778.88</v>
+        <v>1788.07</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1883.52</v>
+        <v>1893.25</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>101.88</v>
+        <v>101.45</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>642.1</v>
+        <v>639.39</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1290.75</v>
+        <v>1285.31</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1171.61</v>
+        <v>1182.27</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>611.28</v>
+        <v>616.84</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>101.88</v>
+        <v>102.55</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1712.26</v>
+        <v>1723.53</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>7131.55</v>
+        <v>7178.52</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2568.39</v>
+        <v>2585.3</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1290.75</v>
+        <v>1299.25</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>509.4</v>
+        <v>513.9299999999999</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3218.02</v>
+        <v>3212.51</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>755.8099999999999</v>
+        <v>754.52</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1284.19</v>
+        <v>1282.87</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1058.56</v>
+        <v>1057.47</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>423.42</v>
+        <v>420.39</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>5373.82</v>
+        <v>5335.33</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1270.27</v>
+        <v>1261.17</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1270.27</v>
+        <v>1261.17</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1511.62</v>
+        <v>1500.79</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1270.27</v>
+        <v>1261.17</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1511.62</v>
+        <v>1500.79</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1270.27</v>
+        <v>1261.17</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1259.69</v>
+        <v>1257.83</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1181.44</v>
+        <v>1175.01</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>468.32</v>
+        <v>465.77</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2279.86</v>
+        <v>2267.44</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1192.08</v>
+        <v>1185.06</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>101.33</v>
+        <v>100.73</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1635.87</v>
+        <v>1626.23</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>384.21</v>
+        <v>384.58</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>101.6</v>
+        <v>101.7</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>168.45</v>
+        <v>175.89</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>4585.57</v>
+        <v>4603.65</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1609.83</v>
+        <v>1616.17</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2406.44</v>
+        <v>2415.92</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1014.68</v>
+        <v>1018.68</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>714.23</v>
+        <v>726</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>149.49</v>
+        <v>147.56</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2512.38</v>
+        <v>2557.93</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1004.95</v>
+        <v>1023.17</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>209.37</v>
+        <v>213.16</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>418.73</v>
+        <v>426.32</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1046.83</v>
+        <v>1063.22</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>641.28</v>
+        <v>641.25</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>896.92</v>
+        <v>892.91</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>152.63</v>
+        <v>151.94</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1271.88</v>
+        <v>1277.13</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>814</v>
+        <v>817.37</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>5425.84</v>
+        <v>5363.2</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>467.86</v>
+        <v>462.46</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1794.36</v>
+        <v>1773.65</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2345.1</v>
+        <v>2318.03</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>3607.04</v>
+        <v>3586.32</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>151.84</v>
+        <v>150.97</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>765.58</v>
+        <v>762.29</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1518.41</v>
+        <v>1511.87</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2277.61</v>
+        <v>2267.8</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1275.97</v>
+        <v>1270.48</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1063.31</v>
+        <v>1047.93</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>506.14</v>
+        <v>498.81</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2740.2</v>
+        <v>2700.56</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1747.54</v>
+        <v>1722.26</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2132.12</v>
+        <v>2086.25</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>202.98</v>
+        <v>198.61</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>639.64</v>
+        <v>625.87</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>682.28</v>
+        <v>666.4</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1467.8</v>
+        <v>1433.64</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>6154.86</v>
+        <v>5958.6</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>388.91</v>
+        <v>376.51</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1382.8</v>
+        <v>1338.71</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>3210.86</v>
+        <v>3126.31</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>577.02</v>
+        <v>561.83</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>514.0700000000001</v>
+        <v>500.54</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>425.95</v>
+        <v>414.73</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>249.69</v>
+        <v>243.12</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>5484.26</v>
+        <v>5384.81</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3147.39</v>
+        <v>3156.55</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1678.61</v>
+        <v>1683.5</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>565.65</v>
+        <v>568</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>629.48</v>
+        <v>632.09</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>245.98</v>
+        <v>248.07</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>2090.85</v>
+        <v>2108.59</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>4040.28</v>
+        <v>4033.53</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1243.16</v>
+        <v>1241.09</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1041.71</v>
+        <v>1039.97</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>491.96</v>
+        <v>491.14</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1537.39</v>
+        <v>1556.31</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>614.96</v>
+        <v>622.52</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1653.66</v>
+        <v>1674.01</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>3100.62</v>
+        <v>3141.08</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>765.13</v>
+        <v>775.12</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>6697.07</v>
+        <v>6861.88</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2731.52</v>
+        <v>2798.74</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>242.8</v>
+        <v>248.78</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>255.04</v>
+        <v>261.32</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1257.94</v>
+        <v>1281.73</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1106.92</v>
+        <v>1119.51</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2577.25</v>
+        <v>2606.56</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1595.44</v>
+        <v>1613.58</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>516.77</v>
+        <v>521.42</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1550.31</v>
+        <v>1564.27</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1607.33</v>
+        <v>1617.61</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>577.63</v>
+        <v>579.45</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>896.59</v>
+        <v>899.41</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1506.87</v>
+        <v>1511.61</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2550.43</v>
+        <v>2558.46</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>3035.02</v>
+        <v>3044.57</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>298.86</v>
+        <v>300.1</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>602.75</v>
+        <v>605.25</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>3340.23</v>
+        <v>3354.08</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>301.37</v>
+        <v>302.62</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>803.67</v>
+        <v>807</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2689.77</v>
+        <v>2695.34</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1506.87</v>
+        <v>1500.4</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1275.22</v>
+        <v>1269.74</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>336.13</v>
+        <v>334.12</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>770.36</v>
+        <v>765.74</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1527.87</v>
+        <v>1507.1</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1283.93</v>
+        <v>1272.97</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1791.55</v>
+        <v>1776.27</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1438</v>
+        <v>1445.74</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>3081.42</v>
+        <v>3098.01</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>3666.89</v>
+        <v>3686.64</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1507.29</v>
+        <v>1515.41</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1912.99</v>
+        <v>1923.29</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>3081.42</v>
+        <v>3098.01</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1786.02</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>664.1799999999999</v>
+        <v>671.6</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>478.31</v>
+        <v>481.94</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>365.3</v>
+        <v>368.06</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1660.44</v>
+        <v>1666.73</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>797.01</v>
+        <v>800.03</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>669.76</v>
+        <v>668.0700000000001</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>4360.23</v>
+        <v>4349.22</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>893.01</v>
+        <v>890.76</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>996.26</v>
+        <v>1003.69</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2284.77</v>
+        <v>2301.79</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2988.79</v>
+        <v>3011.06</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>762.67</v>
+        <v>768.35</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1116.26</v>
+        <v>1105.13</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>6641.77</v>
+        <v>6575.53</v>
       </c>
     </row>
     <row r="189">
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1114.54</v>
+        <v>1111.79</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>855-70-CM26</t>
+          <t>3704-127-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12037,13 +12037,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>394.53</v>
+        <v>881.91</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3704-127-CM26</t>
+          <t>855-70-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>884.1</v>
+        <v>393.55</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>797.01</v>
+        <v>800.9299999999999</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1660.44</v>
+        <v>1668.6</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>828.84</v>
+        <v>832.91</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>263.02</v>
+        <v>264.31</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>6630.74</v>
+        <v>6663.31</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1657.68</v>
+        <v>1665.83</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1709.62</v>
+        <v>1718.02</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>2104.15</v>
+        <v>2114.49</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>6575.48</v>
+        <v>6607.78</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1768.2</v>
+        <v>1774.06</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>552.5599999999999</v>
+        <v>554.39</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>657.55</v>
+        <v>659.64</v>
       </c>
     </row>
     <row r="204">
@@ -12891,13 +12891,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>685.13</v>
+        <v>688.77</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>902977-16-CM26</t>
+          <t>1069-58-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12952,13 +12952,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>328.86</v>
+        <v>1653.06</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1069-58-CM26</t>
+          <t>902977-16-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1644.32</v>
+        <v>330.61</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2055.39</v>
+        <v>2066.32</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>6575.48</v>
+        <v>6610.44</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>4001.17</v>
+        <v>4022.44</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>291.64</v>
+        <v>295.82</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1089.24</v>
+        <v>1107.66</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>3267.71</v>
+        <v>3322.98</v>
       </c>
     </row>
     <row r="213">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>708</v>
+        <v>719.98</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>4589-271-CM26</t>
+          <t>855-85-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13466,17 +13466,17 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13501,13 +13501,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2188.38</v>
+        <v>410.88</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>3595-240-CM26</t>
+          <t>1038-121-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -13562,13 +13562,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1554.9</v>
+        <v>5869.67</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1038-121-CM26</t>
+          <t>4589-271-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13588,17 +13588,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13623,13 +13623,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>5914.54</v>
+        <v>2171.78</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>855-85-CM26</t>
+          <t>3595-240-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13654,12 +13654,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13669,12 +13669,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>414.02</v>
+        <v>1543.11</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2661.54</v>
+        <v>2616.57</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>3230.63</v>
+        <v>3176.05</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>1491.06</v>
+        <v>1469.9</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>795.23</v>
+        <v>783.95</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>497.02</v>
+        <v>489.97</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>4186.28</v>
+        <v>4128.76</v>
       </c>
     </row>
     <row r="224">
@@ -14111,13 +14111,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>5741.18</v>
+        <v>5662.3</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>3704-157-CM26</t>
+          <t>855-90-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14137,17 +14137,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14172,13 +14172,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1618.8</v>
+        <v>653.5599999999999</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>855-90-CM26</t>
+          <t>3704-157-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14198,17 +14198,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>657.64</v>
+        <v>1608.77</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>607.05</v>
+        <v>609.8099999999999</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>310.03</v>
+        <v>311.43</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1517.63</v>
+        <v>1540.22</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1805.98</v>
+        <v>1832.87</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>6070.51</v>
+        <v>6160.9</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1504.98</v>
+        <v>1527.39</v>
       </c>
     </row>
     <row r="233">
@@ -14660,13 +14660,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>353.29</v>
+        <v>354.38</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1038-142-CM26</t>
+          <t>855-97-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14686,17 +14686,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>5888.19</v>
+        <v>740.25</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>855-96-CM26</t>
+          <t>3704-173-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14747,17 +14747,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14782,13 +14782,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>494.81</v>
+        <v>1579.19</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>3704-173-CM26</t>
+          <t>1038-142-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14808,17 +14808,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14843,13 +14843,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1583.38</v>
+        <v>5872.62</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>855-97-CM26</t>
+          <t>855-96-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14869,7 +14869,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>742.21</v>
+        <v>493.5</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2944.1</v>
+        <v>2904.88</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>588.8200000000001</v>
+        <v>580.98</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>505.88</v>
+        <v>495.97</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>5937.67</v>
+        <v>5821.45</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>222.66</v>
+        <v>218.3</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1501.02</v>
+        <v>1478.78</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1444.78</v>
+        <v>1415.09</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>238.16</v>
+        <v>233.27</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1504.98</v>
+        <v>1474.05</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>3398.61</v>
+        <v>3430.89</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>2888.81</v>
+        <v>2916.26</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>2888.81</v>
+        <v>2900.09</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1359.44</v>
+        <v>1364.75</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1464.28</v>
+        <v>1479.01</v>
       </c>
     </row>
     <row r="252">
@@ -15819,13 +15819,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1464.28</v>
+        <v>1479.01</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1233613-1330-CM26</t>
+          <t>1233613-1331-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -15880,13 +15880,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>485.52</v>
+        <v>2334.19</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1233613-1323-CM26</t>
+          <t>1069-75-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15906,17 +15906,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15941,13 +15941,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2888.81</v>
+        <v>1386.51</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1233613-1331-CM26</t>
+          <t>1233613-1330-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -16002,13 +16002,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>2311.05</v>
+        <v>490.38</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1069-75-CM26</t>
+          <t>1233613-1323-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16028,17 +16028,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16063,13 +16063,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1372.76</v>
+        <v>2917.74</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>3595-286-CM26</t>
+          <t>902977-18-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16089,17 +16089,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16109,12 +16109,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -16124,13 +16124,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2098.35</v>
+        <v>643.89</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>5147-197-CM26</t>
+          <t>902977-19-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16185,13 +16185,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>823.66</v>
+        <v>482.91</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>855-104-CM26</t>
+          <t>5147-196-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16246,13 +16246,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>217.81</v>
+        <v>2975.68</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>902977-19-CM26</t>
+          <t>5147-197-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>480.47</v>
+        <v>827.85</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>902977-18-CM26</t>
+          <t>3595-286-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16333,17 +16333,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16353,12 +16353,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -16368,13 +16368,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>640.62</v>
+        <v>2109.05</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5147-196-CM26</t>
+          <t>855-104-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16399,12 +16399,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>2960.59</v>
+        <v>218.92</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>1542.58</v>
+        <v>1548.58</v>
       </c>
     </row>
     <row r="264">
@@ -16551,13 +16551,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>366.07</v>
+        <v>367.49</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>3268-438-CM26</t>
+          <t>1116007-93-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16577,17 +16577,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16612,13 +16612,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>640.62</v>
+        <v>2526.53</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1116007-93-CM26</t>
+          <t>3268-438-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16638,17 +16638,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>2516.73</v>
+        <v>643.12</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>2722.64</v>
+        <v>2708.85</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>5445.29</v>
+        <v>5417.7</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>458.66</v>
+        <v>461.65</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1364.52</v>
+        <v>1373.41</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>5394.16</v>
+        <v>5406.53</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1375.98</v>
+        <v>1385.19</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1419.1</v>
+        <v>1428.6</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>458.66</v>
+        <v>461.73</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1467.72</v>
+        <v>1477.99</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>229.33</v>
+        <v>230.94</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>5458.07</v>
+        <v>5496.27</v>
       </c>
     </row>
     <row r="278">
@@ -17405,13 +17405,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>463.94</v>
+        <v>462.47</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>855-114-CM26</t>
+          <t>855-113-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>543.51</v>
+        <v>144.16</v>
       </c>
     </row>
     <row r="280">
@@ -17527,13 +17527,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1467.72</v>
+        <v>1464.52</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>855-113-CM26</t>
+          <t>855-114-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>144.48</v>
+        <v>542.33</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>545.8099999999999</v>
+        <v>544.62</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1746.58</v>
+        <v>1742.78</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>5458.07</v>
+        <v>5447.13</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>1490.94</v>
+        <v>1487.95</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2729.04</v>
+        <v>2713.24</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1435.72</v>
+        <v>1427.41</v>
       </c>
     </row>
     <row r="288">
@@ -18015,13 +18015,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>545.8099999999999</v>
+        <v>537</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>855-119-CM26</t>
+          <t>796297-64-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18046,12 +18046,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Division de Bienestar Social</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>466.18</v>
+        <v>1557.46</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>796297-64-CM26</t>
+          <t>855-119-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18107,12 +18107,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1582.84</v>
+        <v>458.71</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>958479-184-CM26</t>
+          <t>1470-31-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18168,12 +18168,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>61.980.720-0</t>
+          <t>60.511.124-6</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO CRISTINA CALDERON DE PUERTO WILLIAMS</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18198,13 +18198,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>2797.08</v>
+        <v>556.3200000000001</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1536-156-CM26</t>
+          <t>4589-345-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18229,12 +18229,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>60.511.123-8</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL F</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18259,13 +18259,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>5611.46</v>
+        <v>1339.28</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>4589-345-CM26</t>
+          <t>958479-184-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18290,12 +18290,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>61.980.720-0</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>HOSPITAL COMUNITARIO CRISTINA CALDERON DE PUERTO WILLIAMS</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18305,12 +18305,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
@@ -18320,13 +18320,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1346.75</v>
+        <v>2781.58</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1470-31-CM26</t>
+          <t>1536-156-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18351,12 +18351,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>60.511.124-6</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL F</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18366,12 +18366,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
@@ -18381,13 +18381,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>559.42</v>
+        <v>5580.35</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>5147-230-CM26</t>
+          <t>1470-32-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18412,12 +18412,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>60.511.124-6</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18442,13 +18442,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>3100.1</v>
+        <v>208.75</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>902977-20-CM26</t>
+          <t>1233613-1441-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18468,17 +18468,17 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18503,13 +18503,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>466.18</v>
+        <v>2760.14</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1233613-1441-CM26</t>
+          <t>1233613-1446-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18529,7 +18529,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -18564,13 +18564,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2773.77</v>
+        <v>1391.66</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1233613-1446-CM26</t>
+          <t>5147-230-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18595,12 +18595,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18625,13 +18625,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>1398.54</v>
+        <v>3084.86</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1470-32-CM26</t>
+          <t>902977-20-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -18656,12 +18656,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>60.511.124-6</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LA ANTÁRTICA CHILENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>209.78</v>
+        <v>463.89</v>
       </c>
     </row>
     <row r="300">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>702.49</v>
+        <v>707.2</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1116007-109-CM26</t>
+          <t>3704-223-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -18778,12 +18778,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -18808,13 +18808,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>3729.44</v>
+        <v>1508.68</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>3704-223-CM26</t>
+          <t>1116007-109-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -18839,12 +18839,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18869,7 +18869,68 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1498.65</v>
+        <v>3754.41</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>1079445-563-CM26</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>60.505.628-8</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M303" s="2" t="n">
+        <v>525.24</v>
       </c>
     </row>
   </sheetData>
